--- a/Files/TestCase.xlsx
+++ b/Files/TestCase.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="19">
   <si>
     <t>Scenarios</t>
   </si>
@@ -41,18 +42,24 @@
     <t>Add Employee</t>
   </si>
   <si>
+    <t>launch&amp;login</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>addEmployeeData</t>
+  </si>
+  <si>
+    <t>logout</t>
+  </si>
+  <si>
+    <t>Add Job Vacancy</t>
+  </si>
+  <si>
     <t>login</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>addEmployeeData</t>
-  </si>
-  <si>
-    <t>Add Job Vacancy</t>
-  </si>
-  <si>
     <t>addJobVacancy</t>
   </si>
   <si>
@@ -60,6 +67,24 @@
   </si>
   <si>
     <t>addCandidateData</t>
+  </si>
+  <si>
+    <t>Add Product To Wishlist</t>
+  </si>
+  <si>
+    <t>addProductToWishlist</t>
+  </si>
+  <si>
+    <t>Add Product to Cart</t>
+  </si>
+  <si>
+    <t>addProductToCart</t>
+  </si>
+  <si>
+    <t>Order an Item</t>
+  </si>
+  <si>
+    <t>orderAnItem</t>
   </si>
 </sst>
 </file>
@@ -694,12 +719,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1019,8 +1043,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="25.3611111111111" customWidth="1"/>
     <col min="2" max="3" width="26.2222222222222" customWidth="1"/>
@@ -1059,12 +1083,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="12" customHeight="1" spans="1:3">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -1072,10 +1096,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>5</v>
@@ -1083,10 +1107,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
@@ -1094,22 +1118,177 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="22.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="20.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="12.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>